--- a/data/chinese/P3T1_Chapter6.xlsx
+++ b/data/chinese/P3T1_Chapter6.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/homes/ximonlam/Mac/單詞複習網素材/Chinese/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CC2B585-EABA-704C-9859-34AC50F73F8E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2833B2CC-0C38-EC4F-AA4F-31914ACCAFC7}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="25600" yWindow="460" windowWidth="38400" windowHeight="21140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="37">
   <si>
     <t>生字</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -59,9 +59,6 @@
   <si>
     <t>暫沒有必懂寫生字</t>
     <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>詞語</t>
   </si>
   <si>
     <t>解釋</t>
@@ -555,13 +552,13 @@
   <sheetData>
     <row r="1" spans="1:11" ht="27">
       <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>9</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>10</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>2</v>
@@ -576,13 +573,13 @@
     </row>
     <row r="2" spans="1:11" ht="27">
       <c r="A2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="C2" s="3" t="s">
         <v>12</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>13</v>
       </c>
       <c r="D2" s="3">
         <v>1</v>
@@ -591,13 +588,13 @@
     </row>
     <row r="3" spans="1:11" ht="27">
       <c r="A3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="C3" s="3" t="s">
         <v>15</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>16</v>
       </c>
       <c r="D3" s="3">
         <v>1</v>
@@ -606,13 +603,13 @@
     </row>
     <row r="4" spans="1:11" ht="27">
       <c r="A4" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="C4" s="3" t="s">
         <v>18</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>19</v>
       </c>
       <c r="D4" s="3">
         <v>1</v>
@@ -621,13 +618,13 @@
     </row>
     <row r="5" spans="1:11" ht="27">
       <c r="A5" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="C5" s="3" t="s">
         <v>21</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>22</v>
       </c>
       <c r="D5" s="3">
         <v>1</v>
@@ -636,13 +633,13 @@
     </row>
     <row r="6" spans="1:11" ht="27">
       <c r="A6" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="C6" s="3" t="s">
         <v>24</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>25</v>
       </c>
       <c r="D6" s="3">
         <v>2</v>
@@ -651,13 +648,13 @@
     </row>
     <row r="7" spans="1:11" ht="27">
       <c r="A7" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="C7" s="3" t="s">
         <v>27</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>28</v>
       </c>
       <c r="D7" s="3">
         <v>2</v>
@@ -666,13 +663,13 @@
     </row>
     <row r="8" spans="1:11" ht="27">
       <c r="A8" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="C8" s="3" t="s">
         <v>30</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>31</v>
       </c>
       <c r="D8" s="3">
         <v>2</v>
@@ -681,13 +678,13 @@
     </row>
     <row r="9" spans="1:11" ht="27">
       <c r="A9" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="C9" s="3" t="s">
         <v>33</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>34</v>
       </c>
       <c r="D9" s="3">
         <v>2</v>
@@ -697,13 +694,13 @@
     </row>
     <row r="10" spans="1:11" ht="27">
       <c r="A10" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="C10" s="3" t="s">
         <v>36</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>37</v>
       </c>
       <c r="D10" s="3">
         <v>2</v>
